--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.3286954287471</v>
+        <v>5.253413007171403</v>
       </c>
       <c r="D2" t="n">
-        <v>32.49873576689791</v>
+        <v>5.28104456212091</v>
       </c>
       <c r="E2" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F2" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.76448357891445</v>
+        <v>7.274228581573598</v>
       </c>
       <c r="D3" t="n">
-        <v>45.52120190299937</v>
+        <v>7.397195309237398</v>
       </c>
       <c r="E3" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F3" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.09814866233192</v>
+        <v>7.653449157628938</v>
       </c>
       <c r="D4" t="n">
-        <v>47.91497212021221</v>
+        <v>7.786182969534484</v>
       </c>
       <c r="E4" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F4" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.94822448696947</v>
+        <v>3.566586479132539</v>
       </c>
       <c r="D5" t="n">
-        <v>22.74260187336611</v>
+        <v>3.695672804421992</v>
       </c>
       <c r="E5" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F5" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2260298652574</v>
+        <v>1.824229853104328</v>
       </c>
       <c r="D6" t="n">
-        <v>11.72883568048222</v>
+        <v>1.90593579807836</v>
       </c>
       <c r="E6" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F6" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.65794118567509</v>
+        <v>8.881915442672202</v>
       </c>
       <c r="D7" t="n">
-        <v>55.61277801787185</v>
+        <v>9.037076427904177</v>
       </c>
       <c r="E7" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F7" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.93007362041665</v>
+        <v>1.938636963317705</v>
       </c>
       <c r="D8" t="n">
-        <v>11.91835004945041</v>
+        <v>1.936731883035691</v>
       </c>
       <c r="E8" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F8" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.29446679890679</v>
+        <v>3.785350854822353</v>
       </c>
       <c r="D9" t="n">
-        <v>23.05103733759297</v>
+        <v>3.745793567358858</v>
       </c>
       <c r="E9" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F9" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.17499055177366</v>
+        <v>2.79093596466322</v>
       </c>
       <c r="D10" t="n">
-        <v>12.67164041215552</v>
+        <v>2.059141566975272</v>
       </c>
       <c r="E10" t="n">
-        <v>15.17885247033915</v>
+        <v>2.466563526430112</v>
       </c>
       <c r="F10" t="n">
-        <v>15.92223294291616</v>
+        <v>2.587362853223876</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
